--- a/makina-drive/Assets/EasyWaveData.xlsx
+++ b/makina-drive/Assets/EasyWaveData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repository\makina-drive\makina-drive\Assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A751B711-0A6D-4163-AA1A-3E6AB8C32ABC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F20EE80-11F2-4ECD-BFF1-EECD6E844723}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2172" yWindow="3360" windowWidth="20316" windowHeight="8880" xr2:uid="{B15D334C-B6D0-405E-AAFF-F85EF3C9ECB4}"/>
   </bookViews>
@@ -283,7 +283,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1494" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1494" uniqueCount="200">
   <si>
     <t>Wave1</t>
   </si>
@@ -1730,13 +1730,6 @@
   </si>
   <si>
     <t>MaxHP:1.4:0;ATK:1.3:0,Speed:1.2:0,DashSpeed:1.2:0</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>MaxHP:1.6:0;ATK:1.3:5,Speed:1.3:0,DashSpeed:1.3:0</t>
-  </si>
-  <si>
-    <t>MaxHP:1.6:0;ATK:1.3:5,Speed:1.3:0,DashSpeed:1.3:0</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -5823,7 +5816,7 @@
         <v>181</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C37" s="8">
         <v>59</v>
@@ -5919,7 +5912,7 @@
         <v>0.5</v>
       </c>
       <c r="M38" s="13" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="N38" s="13">
         <v>13</v>
@@ -5978,7 +5971,7 @@
         <v>0.5</v>
       </c>
       <c r="M39" s="8" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="N39" s="8">
         <v>13</v>
@@ -6041,7 +6034,7 @@
         <v>0.5</v>
       </c>
       <c r="M40" s="8" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="N40" s="8">
         <v>13</v>
@@ -6100,7 +6093,7 @@
         <v>0.5</v>
       </c>
       <c r="M41" s="8" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="N41" s="8">
         <v>13</v>
@@ -6159,7 +6152,7 @@
         <v>0.5</v>
       </c>
       <c r="M42" s="8" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="N42" s="8">
         <v>13</v>
@@ -6281,7 +6274,7 @@
         <v>0.5</v>
       </c>
       <c r="M44" s="8" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="N44" s="8">
         <v>13</v>
@@ -6338,7 +6331,7 @@
         <v>0.5</v>
       </c>
       <c r="M45" s="8" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="N45" s="8">
         <v>13</v>
@@ -6395,7 +6388,7 @@
         <v>0.5</v>
       </c>
       <c r="M46" s="8" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="N46" s="8">
         <v>13</v>
@@ -6454,7 +6447,7 @@
         <v>0.5</v>
       </c>
       <c r="M47" s="8" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="N47" s="8">
         <v>13</v>
@@ -6519,7 +6512,7 @@
         <v>0.5</v>
       </c>
       <c r="M48" s="8" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="N48" s="8">
         <v>13</v>
@@ -6578,7 +6571,7 @@
         <v>0.5</v>
       </c>
       <c r="M49" s="8" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="N49" s="8">
         <v>13</v>
@@ -6637,7 +6630,7 @@
         <v>0.5</v>
       </c>
       <c r="M50" s="8" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="N50" s="8">
         <v>13</v>
@@ -6700,7 +6693,7 @@
         <v>0.5</v>
       </c>
       <c r="M51" s="13" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="N51" s="13">
         <v>20</v>
@@ -6759,7 +6752,7 @@
         <v>0.5</v>
       </c>
       <c r="M52" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="N52" s="8">
         <v>20</v>
@@ -6822,7 +6815,7 @@
         <v>0.5</v>
       </c>
       <c r="M53" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="N53" s="8">
         <v>20</v>
@@ -6863,7 +6856,7 @@
         <v>102</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H54" s="8">
         <v>6</v>
@@ -6881,7 +6874,7 @@
         <v>0.5</v>
       </c>
       <c r="M54" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="N54" s="8">
         <v>20</v>
@@ -6946,7 +6939,7 @@
         <v>0.5</v>
       </c>
       <c r="M55" s="8" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="N55" s="8">
         <v>20</v>
@@ -7011,7 +7004,7 @@
         <v>0.5</v>
       </c>
       <c r="M56" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="N56" s="8">
         <v>20</v>
@@ -7070,7 +7063,7 @@
         <v>0.5</v>
       </c>
       <c r="M57" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="N57" s="8">
         <v>20</v>
@@ -7111,7 +7104,7 @@
         <v>81</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="H58" s="8">
         <v>4</v>
@@ -7129,7 +7122,7 @@
         <v>0.5</v>
       </c>
       <c r="M58" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="N58" s="8">
         <v>20</v>
@@ -7192,7 +7185,7 @@
         <v>0.5</v>
       </c>
       <c r="M59" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="N59" s="8">
         <v>20</v>
@@ -7251,7 +7244,7 @@
         <v>0.5</v>
       </c>
       <c r="M60" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="N60" s="8">
         <v>20</v>
@@ -7310,7 +7303,7 @@
         <v>0.5</v>
       </c>
       <c r="M61" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="N61" s="8">
         <v>20</v>
@@ -7369,7 +7362,7 @@
         <v>0.5</v>
       </c>
       <c r="M62" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="N62" s="8">
         <v>20</v>
@@ -7416,7 +7409,7 @@
         <v>81</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="H63" s="8">
         <v>4</v>
@@ -7434,7 +7427,7 @@
         <v>0.5</v>
       </c>
       <c r="M63" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="N63" s="8">
         <v>20</v>
@@ -7497,7 +7490,7 @@
         <v>0.5</v>
       </c>
       <c r="M64" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="N64" s="8">
         <v>20</v>
@@ -7556,7 +7549,7 @@
         <v>0.5</v>
       </c>
       <c r="M65" s="8" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="N65" s="8">
         <v>20</v>
@@ -7606,10 +7599,10 @@
         <v>144</v>
       </c>
       <c r="H66" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I66" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J66" s="8">
         <v>0</v>
@@ -7621,7 +7614,7 @@
         <v>0.5</v>
       </c>
       <c r="M66" s="8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="N66" s="8">
         <v>20</v>
